--- a/lcr_analyses/clustering/carriers/LCRFinder/cluster_summaries_pam.xlsx
+++ b/lcr_analyses/clustering/carriers/LCRFinder/cluster_summaries_pam.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4522,4 +4526,5818 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>218</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.03825250836120402</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1605504587155963</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1238532110091743</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3165137614678899</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1972477064220184</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5688073394495413</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03211009174311927</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.009174311926605505</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2201834862385321</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.04587155963302753</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01376146788990826</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.07339449541284404</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.08256880733944955</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2844036697247707</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2522935779816514</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.03211009174311927</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.004587155963302753</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9311926605504587</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.04128440366972477</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.004587155963302753</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.01376146788990826</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.01834862385321101</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.217948717948718</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.07275132275132275</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8752834467120181</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2916666666666666</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>121</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>217</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05795148247978436</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2258064516129032</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1751152073732719</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6267281105990783</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.271889400921659</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7649769585253456</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02764976958525346</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.119815668202765</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.184331797235023</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3824884792626728</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9124423963133641</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.08294930875576037</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1013824884792627</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2119815668202765</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1566820276497696</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.004608294930875576</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.004608294930875576</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.783410138248848</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.08294930875576037</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.009216589861751152</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7565217391304347</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3786407766990291</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05625</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.845679012345679</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2627118644067797</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5526315789473685</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.03076923076923077</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1521739130434782</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.02914798206278027</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6.428571428571429</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1443298969072165</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1237113402061856</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2474226804123711</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1649484536082474</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6185567010309279</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1443298969072165</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07216494845360824</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.979381443298969</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.06185567010309279</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.04123711340206185</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.134020618556701</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01030927835051546</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01030927835051546</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01030927835051546</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.6964285714285714</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>161</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1015965166908563</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2236024844720497</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1863354037267081</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8633540372670807</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2360248447204969</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8385093167701864</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1180124223602484</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.124223602484472</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6645962732919255</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2546583850931677</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02484472049689441</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1118012422360248</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1863354037267081</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2546583850931677</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02484472049689441</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.04968944099378882</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.006211180124223602</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.09316770186335403</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1055900621118012</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4202898550724637</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.04819277108433734</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.01176470588235294</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9012345679012346</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1491228070175439</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0196078431372549</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01390711967194766</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2428571428571429</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8714285714285714</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1285714285714286</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1909090909090909</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.8490028490028489</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.5523809523809524</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.3489130434782609</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>112</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03363482193329564</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1339285714285714</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3035714285714285</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1607142857142857</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5089285714285714</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.05357142857142857</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4196428571428572</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6339285714285714</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02678571428571428</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01785714285714286</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.04464285714285714</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.02678571428571428</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1160714285714286</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02678571428571428</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9547314578005115</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5440038684719535</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.4731371921969939</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2145593869731801</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>133</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04245283018867924</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.066666666666666</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2255639097744361</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2180451127819549</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2706766917293233</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1804511278195489</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6691729323308271</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03007518796992481</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06766917293233082</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2406015037593985</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9699248120300752</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.07518796992481203</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.112781954887218</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1278195488721804</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.007518796992481203</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.007518796992481203</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7819548872180451</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.09774436090225563</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.007518796992481203</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.01503759398496241</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.1203007518796992</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5267857142857143</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4260869565217391</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.09803921568627451</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1879194630872483</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.08064516129032258</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>119</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02521008403361345</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09243697478991597</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1260504201680672</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2689075630252101</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.226890756302521</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.02521008403361345</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03361344537815126</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1680672268907563</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05042016806722689</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1008403361344538</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2436974789915966</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.05042016806722689</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8487394957983193</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.06722689075630252</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01680672268907563</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.02521008403361345</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9448818897637795</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>213</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05900816070307596</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2206572769953052</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1737089201877934</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6338028169014085</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2769953051643192</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7746478873239436</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02816901408450704</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1220657276995305</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1877934272300469</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.812206572769953</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3896713615023474</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.92018779342723</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.08450704225352113</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.09859154929577464</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2065727699530517</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1596244131455399</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.004694835680751174</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.004694835680751174</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7793427230046949</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.08450704225352113</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.03286384976525822</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.009389671361502348</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03286384976525822</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.09859154929577464</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7596153846153846</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3755458515283843</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.05625</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8444444444444444</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2648648648648649</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5609756097560976</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.03076923076923077</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>129</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03416149068322982</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2170542635658915</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1007751937984496</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2248062015503876</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1782945736434109</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.007751937984496124</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1472868217054264</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0310077519379845</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.124031007751938</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1162790697674419</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7209302325581395</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.124031007751938</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0310077519379845</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9302325581395349</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.08527131782945736</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.03875968992248062</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.04651162790697674</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>178</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1029072006160955</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.545454545454546</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2415730337078652</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2134831460674157</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8707865168539326</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2584269662921349</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8370786516853933</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2022471910112359</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1067415730337079</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3370786516853932</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1179775280898876</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.601123595505618</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2359550561797753</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.07865168539325842</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.151685393258427</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3089887640449438</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8820224719101124</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.08426966292134831</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.09550561797752809</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3892773892773893</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5027472527472527</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05348693910785414</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.01408450704225352</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1344632768361582</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.01335470085470086</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1651515151515152</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3981132075471698</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>118</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02929838087895143</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1473684210526316</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2526315789473684</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.631578947368421</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03157894736842105</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1473684210526316</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.07368421052631578</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9894736842105263</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.06315789473684211</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.04210526315789474</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03157894736842105</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01052631578947368</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01052631578947368</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.01052631578947368</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03363482193329564</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1203703703703704</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5277777777777778</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6481481481481481</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1296296296296296</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.04629629629629629</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9547314578005115</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5505050505050505</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>119</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04334365325077399</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2436974789915966</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.226890756302521</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2773109243697479</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1932773109243698</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03361344537815126</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.06722689075630252</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2521008403361344</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6050420168067226</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9831932773109243</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.08403361344537816</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1008403361344538</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7983193277310925</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1092436974789916</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.008403361344537815</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4117647058823529</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1759259259259259</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.348993288590604</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.1020408163265306</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01302083333333333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1914893617021277</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3191489361702128</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3191489361702128</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>120</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02501638953453722</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09166666666666666</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1166666666666667</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1916666666666667</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.008333333333333333</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1083333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.09166666666666666</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.2416666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.008333333333333333</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.9528508771929824</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>190</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05685098662390504</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2315789473684211</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6263157894736842</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2684210526315789</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7947368421052632</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03684210526315789</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1789473684210526</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9421052631578948</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.09473684210526316</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.08421052631578947</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2210526315789474</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1631578947368421</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.005263157894736842</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.005263157894736842</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7631578947368421</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.09473684210526316</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.03684210526315789</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.01052631578947368</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03684210526315789</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.09473684210526316</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7396011396011396</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3889995022399204</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8342490842490843</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2330316742081448</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.3139880952380952</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5553855569155447</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.05476694292599776</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1354895104895105</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>129</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.03416149068322982</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2170542635658915</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1007751937984496</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2248062015503876</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1782945736434109</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7441860465116279</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.007751937984496124</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1472868217054264</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0310077519379845</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.124031007751938</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1162790697674419</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7209302325581395</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.124031007751938</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0310077519379845</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9302325581395349</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.08527131782945736</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.03875968992248062</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.04651162790697674</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8043478260869565</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>179</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08754208754208755</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.217877094972067</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2067039106145251</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7988826815642458</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3016759776536313</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8100558659217877</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2122905027932961</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0223463687150838</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3519553072625698</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.09497206703910614</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6089385474860335</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2346368715083799</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02793296089385475</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.06145251396648044</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1396648044692737</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2849162011173184</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.0111731843575419</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.0111731843575419</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8044692737430168</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.0335195530726257</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.00558659217877095</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.00558659217877095</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0782122905027933</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.0782122905027933</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3818181818181818</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9107142857142857</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1355932203389831</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.08433734939759036</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>112</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02942751556262842</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9895833333333334</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.9354166666666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.6982142857142857</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.8186274509803921</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.6458333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>61</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.02300884955752212</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2786885245901639</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1639344262295082</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.180327868852459</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1475409836065574</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.360655737704918</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.819672131147541</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2786885245901639</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1475409836065574</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5897435897435898</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>124</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04233154309915554</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.958333333333334</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.217741935483871</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2661290322580645</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1935483870967742</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7016129032258065</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1693548387096774</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2338709677419355</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6209677419354839</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.08064516129032258</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1048387096774194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7983870967741935</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1451612903225807</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.717741935483871</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1048387096774194</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.008064516129032258</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5441558441558441</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7443099273607748</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1188235294117647</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.07953826691967109</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1748686096512184</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>47</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01302083333333333</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1914893617021277</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3191489361702128</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3191489361702128</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1063829787234043</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02127659574468085</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0425531914893617</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>62</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1676265270506108</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8064516129032258</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1451612903225807</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8870967741935484</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4032258064516129</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.04838709677419355</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1129032258064516</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.890116512655685</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1849358974358974</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.0217670011148272</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.01450869474125288</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.930952380952381</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.4438717067583047</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.07783161720169594</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5084483244156576</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>47</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>91</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.07279344858962693</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1868131868131868</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.3736263736263736</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3186813186813187</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6813186813186813</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03296703296703297</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6703296703296703</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1318681318681319</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1758241758241758</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.03296703296703297</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1648351648351648</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1318681318681319</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.01098901098901099</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.7582417582417582</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.05494505494505494</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03296703296703297</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4025974025974026</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8735632183908046</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.04081632653061224</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>188</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.05625436636669871</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6.366071428571429</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2287234042553191</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1968085106382979</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6223404255319149</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2606382978723404</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7819148936170213</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.03723404255319149</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.05319148936170213</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1648936170212766</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7978723404255319</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3723404255319149</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9468085106382979</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.09574468085106383</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2234042553191489</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1436170212765958</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.005319148936170213</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.005319148936170213</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7606382978723404</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.0797872340425532</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.02659574468085106</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.005319148936170213</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03723404255319149</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.09042553191489362</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7415824915824916</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.06594202898550725</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8358516483516484</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.3224958163997131</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5595575723199093</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.05649897854954035</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.133974358974359</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>73</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.01808318264014467</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.08955223880597014</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1492537313432836</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3582089552238806</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2388059701492537</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1194029850746269</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.04477611940298507</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.05970149253731343</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9552238805970149</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>154</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0859477817873063</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.148351648351649</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1688311688311688</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7922077922077922</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2337662337662338</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01948051948051948</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2337662337662338</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6948051948051948</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2402597402597403</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01948051948051948</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.05844155844155844</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2012987012987013</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8311688311688312</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.03896103896103896</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.06493506493506493</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.08441558441558442</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.3777777777777778</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.530952380952381</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.04205332154956547</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9186431329288473</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1441558441558441</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.01283903065318568</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1929280397022332</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.1022388059701493</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.3817081525462435</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>93</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>114</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.03181682111297267</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2192982456140351</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.09649122807017543</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2280701754385965</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7017543859649122</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.008771929824561403</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1140350877192982</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.131578947368421</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7631578947368421</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9385964912280702</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.1140350877192982</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04385964912280702</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.06140350877192982</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2214452214452214</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.6587701612903225</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.02127659574468084</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>63</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.02300884955752212</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2698412698412698</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1587301587301587</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3492063492063492</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.01587301587301587</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1587301587301587</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.5862068965517241</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>122</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.04127151917849592</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.910714285714286</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2459016393442623</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2213114754098361</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.2622950819672131</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.1967213114754098</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6967213114754098</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1475409836065574</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2295081967213115</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6311475409836066</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.9344262295081968</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.07377049180327869</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.7950819672131147</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7131147540983607</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1065573770491803</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.00819672131147541</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.1065573770491803</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1065573770491803</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.42430441898527</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1809090909090909</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7380952380952381</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3514705882352941</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.07953826691967109</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1726708074534161</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>52</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01263599093925472</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0576923076923077</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2884615384615384</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8653846153846154</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.07437070938215104</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8973684210526316</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2052631578947368</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>61</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.819672131147541</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.09836065573770492</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.819672131147541</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.03278688524590164</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8688524590163934</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1311475409836066</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3442622950819672</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8852459016393442</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3934426229508197</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.04918032786885246</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1639344262295082</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01639344262295082</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1147540983606557</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.02173913043478261</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.01550387596899225</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5094339622641509</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.02942751556262842</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1458333333333333</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.9895833333333334</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.9354166666666667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.6982142857142857</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.8186274509803921</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.6458333333333333</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>